--- a/Domain.xlsx
+++ b/Domain.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" r:id="rId6" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="16">
   <si>
     <t>126.com</t>
   </si>
@@ -66,6 +67,15 @@
   </si>
   <si>
     <t>adelaide.edu.au</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>FAILED TO LOAD</t>
   </si>
 </sst>
 </file>
@@ -238,7 +248,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,6 +439,36 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
       </patternFill>
     </fill>
   </fills>
@@ -688,13 +728,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1307,4 +1350,122 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="46.875" customWidth="true"/>
+    <col min="2" max="2" width="31.25" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s" s="3">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/Domain.xlsx
+++ b/Domain.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="16">
   <si>
     <t>126.com</t>
   </si>
@@ -728,13 +728,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="true"/>
@@ -1373,7 +1376,7 @@
       <c r="A2" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="3">
+      <c r="B2" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1381,7 +1384,7 @@
       <c r="A3" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s" s="3">
+      <c r="B3" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1389,7 +1392,7 @@
       <c r="A4" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B4" t="s" s="3">
+      <c r="B4" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1397,7 +1400,7 @@
       <c r="A5" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B5" t="s" s="3">
+      <c r="B5" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1405,7 +1408,7 @@
       <c r="A6" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s" s="3">
+      <c r="B6" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1413,7 +1416,7 @@
       <c r="A7" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="s" s="3">
+      <c r="B7" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1421,7 +1424,7 @@
       <c r="A8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B8" t="s" s="3">
+      <c r="B8" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1429,7 +1432,7 @@
       <c r="A9" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B9" t="s" s="3">
+      <c r="B9" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1437,7 +1440,7 @@
       <c r="A10" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B10" t="s" s="3">
+      <c r="B10" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1445,7 +1448,7 @@
       <c r="A11" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B11" t="s" s="3">
+      <c r="B11" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1453,7 +1456,7 @@
       <c r="A12" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B12" t="s" s="3">
+      <c r="B12" t="s" s="6">
         <v>15</v>
       </c>
     </row>
@@ -1461,7 +1464,7 @@
       <c r="A13" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B13" t="s" s="3">
+      <c r="B13" t="s" s="6">
         <v>15</v>
       </c>
     </row>

--- a/Domain.xlsx
+++ b/Domain.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Results" r:id="rId6" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>126.com</t>
   </si>
@@ -68,15 +67,6 @@
   <si>
     <t>adelaide.edu.au</t>
   </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>FAILED TO LOAD</t>
-  </si>
 </sst>
 </file>
 
@@ -248,7 +238,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,36 +429,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="42"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="42"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="45"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="45"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="43"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
       </patternFill>
     </fill>
   </fills>
@@ -728,19 +688,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1353,122 +1307,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="46.875" customWidth="true"/>
-    <col min="2" max="2" width="31.25" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s" s="6">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/Domain.xlsx
+++ b/Domain.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" r:id="rId6" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>126.com</t>
   </si>
@@ -66,6 +67,39 @@
   </si>
   <si>
     <t>adelaide.edu.au</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>TYPO</t>
+  </si>
+  <si>
+    <t>Likely typo of 163.com</t>
+  </si>
+  <si>
+    <t>SAFE</t>
+  </si>
+  <si>
+    <t>Known legitimate provider</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>Not on any list (probably company domain)</t>
+  </si>
+  <si>
+    <t>DISPOSABLE</t>
+  </si>
+  <si>
+    <t>On disposable-domain blocklist</t>
   </si>
 </sst>
 </file>
@@ -238,7 +272,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,6 +463,36 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
       </patternFill>
     </fill>
   </fills>
@@ -688,13 +752,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1307,4 +1374,162 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="39.0625" customWidth="true"/>
+    <col min="2" max="2" width="15.625" customWidth="true"/>
+    <col min="3" max="3" width="54.6875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="3">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/Domain.xlsx
+++ b/Domain.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Email Verification" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" r:id="rId6" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="612">
   <si>
     <t>ID</t>
   </si>
@@ -945,6 +946,924 @@
   </si>
   <si>
     <t>casey.miller802@invalid.void</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Records</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>INVALID</t>
+  </si>
+  <si>
+    <t>Bad domain syntax</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>300</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +2065,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1361,6 +2280,46 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
       </patternFill>
     </fill>
   </fills>
@@ -1618,7 +2577,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1626,6 +2585,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1982,8 +2945,8 @@
   <dimension ref="A1:C301"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="35.0"/>
+    <col min="3" max="3" customWidth="true" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1998,10 +2961,10 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2009,10 +2972,10 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2020,10 +2983,10 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2031,10 +2994,10 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2042,10 +3005,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -2053,10 +3016,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -2064,10 +3027,10 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2075,10 +3038,10 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -2086,10 +3049,10 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -2097,10 +3060,10 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11">
+      <c r="A11" s="0">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -2108,10 +3071,10 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12">
+      <c r="A12" s="0">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -2119,10 +3082,10 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13">
+      <c r="A13" s="0">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -2130,10 +3093,10 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14">
+      <c r="A14" s="0">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2141,10 +3104,10 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15">
+      <c r="A15" s="0">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2152,10 +3115,10 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16">
+      <c r="A16" s="0">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2163,10 +3126,10 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17">
+      <c r="A17" s="0">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -2174,10 +3137,10 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18">
+      <c r="A18" s="0">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>22</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -2185,10 +3148,10 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19">
+      <c r="A19" s="0">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>23</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -2196,10 +3159,10 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20">
+      <c r="A20" s="0">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2207,10 +3170,10 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21">
+      <c r="A21" s="0">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2218,10 +3181,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22">
+      <c r="A22" s="0">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -2229,10 +3192,10 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23">
+      <c r="A23" s="0">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>27</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2240,10 +3203,10 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24">
+      <c r="A24" s="0">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -2251,10 +3214,10 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25">
+      <c r="A25" s="0">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2262,10 +3225,10 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26">
+      <c r="A26" s="0">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="0">
         <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2273,10 +3236,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27">
+      <c r="A27" s="0">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="0">
         <v>31</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2284,10 +3247,10 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28">
+      <c r="A28" s="0">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="0">
         <v>32</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2295,10 +3258,10 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29">
+      <c r="A29" s="0">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" t="s" s="0">
         <v>33</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -2306,10 +3269,10 @@
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30">
+      <c r="A30" s="0">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2317,10 +3280,10 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31">
+      <c r="A31" s="0">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -2328,10 +3291,10 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32">
+      <c r="A32" s="0">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" t="s" s="0">
         <v>36</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -2339,10 +3302,10 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33">
+      <c r="A33" s="0">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" t="s" s="0">
         <v>37</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -2350,10 +3313,10 @@
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34">
+      <c r="A34" s="0">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2361,10 +3324,10 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35">
+      <c r="A35" s="0">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -2372,10 +3335,10 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36">
+      <c r="A36" s="0">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" t="s" s="0">
         <v>40</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -2383,10 +3346,10 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37">
+      <c r="A37" s="0">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="s" s="0">
         <v>41</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2394,10 +3357,10 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38">
+      <c r="A38" s="0">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" t="s" s="0">
         <v>42</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2405,10 +3368,10 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39">
+      <c r="A39" s="0">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="s" s="0">
         <v>43</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2416,10 +3379,10 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40">
+      <c r="A40" s="0">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2427,10 +3390,10 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41">
+      <c r="A41" s="0">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" t="s" s="0">
         <v>45</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2438,10 +3401,10 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42">
+      <c r="A42" s="0">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="s" s="0">
         <v>46</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2449,10 +3412,10 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43">
+      <c r="A43" s="0">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="s" s="0">
         <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -2460,10 +3423,10 @@
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44">
+      <c r="A44" s="0">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -2471,10 +3434,10 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45">
+      <c r="A45" s="0">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="s" s="0">
         <v>49</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -2482,10 +3445,10 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46">
+      <c r="A46" s="0">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" t="s" s="0">
         <v>50</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -2493,10 +3456,10 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47">
+      <c r="A47" s="0">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" t="s" s="0">
         <v>51</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -2504,10 +3467,10 @@
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48">
+      <c r="A48" s="0">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" t="s" s="0">
         <v>52</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -2515,10 +3478,10 @@
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49">
+      <c r="A49" s="0">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" t="s" s="0">
         <v>53</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -2526,10 +3489,10 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50">
+      <c r="A50" s="0">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" t="s" s="0">
         <v>54</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -2537,10 +3500,10 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51">
+      <c r="A51" s="0">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" t="s" s="0">
         <v>55</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -2548,10 +3511,10 @@
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52">
+      <c r="A52" s="0">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" t="s" s="0">
         <v>56</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -2559,10 +3522,10 @@
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53">
+      <c r="A53" s="0">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" t="s" s="0">
         <v>57</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -2570,10 +3533,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54">
+      <c r="A54" s="0">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" t="s" s="0">
         <v>58</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2581,10 +3544,10 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55">
+      <c r="A55" s="0">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" t="s" s="0">
         <v>59</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -2592,10 +3555,10 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56">
+      <c r="A56" s="0">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="s" s="0">
         <v>60</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -2603,10 +3566,10 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57">
+      <c r="A57" s="0">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" t="s" s="0">
         <v>61</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -2614,10 +3577,10 @@
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58">
+      <c r="A58" s="0">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" t="s" s="0">
         <v>62</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -2625,10 +3588,10 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59">
+      <c r="A59" s="0">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="s" s="0">
         <v>63</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -2636,10 +3599,10 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60">
+      <c r="A60" s="0">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" t="s" s="0">
         <v>64</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -2647,10 +3610,10 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61">
+      <c r="A61" s="0">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" t="s" s="0">
         <v>65</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -2658,10 +3621,10 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62">
+      <c r="A62" s="0">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" t="s" s="0">
         <v>66</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -2669,10 +3632,10 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63">
+      <c r="A63" s="0">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="s" s="0">
         <v>67</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -2680,10 +3643,10 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64">
+      <c r="A64" s="0">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" t="s" s="0">
         <v>68</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -2691,10 +3654,10 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65">
+      <c r="A65" s="0">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" t="s" s="0">
         <v>69</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -2702,10 +3665,10 @@
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66">
+      <c r="A66" s="0">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" t="s" s="0">
         <v>70</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -2713,10 +3676,10 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67">
+      <c r="A67" s="0">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" t="s" s="0">
         <v>71</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -2724,10 +3687,10 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68">
+      <c r="A68" s="0">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" t="s" s="0">
         <v>72</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -2735,10 +3698,10 @@
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69">
+      <c r="A69" s="0">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" t="s" s="0">
         <v>73</v>
       </c>
       <c r="C69" s="4" t="s">
@@ -2746,10 +3709,10 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70">
+      <c r="A70" s="0">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" t="s" s="0">
         <v>74</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -2757,10 +3720,10 @@
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71">
+      <c r="A71" s="0">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" t="s" s="0">
         <v>75</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -2768,10 +3731,10 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72">
+      <c r="A72" s="0">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" t="s" s="0">
         <v>76</v>
       </c>
       <c r="C72" s="3" t="s">
@@ -2779,10 +3742,10 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73">
+      <c r="A73" s="0">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" t="s" s="0">
         <v>77</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -2790,10 +3753,10 @@
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74">
+      <c r="A74" s="0">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" t="s" s="0">
         <v>78</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -2801,10 +3764,10 @@
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75">
+      <c r="A75" s="0">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" t="s" s="0">
         <v>79</v>
       </c>
       <c r="C75" s="4" t="s">
@@ -2812,10 +3775,10 @@
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76">
+      <c r="A76" s="0">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" t="s" s="0">
         <v>80</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -2823,10 +3786,10 @@
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77">
+      <c r="A77" s="0">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" t="s" s="0">
         <v>81</v>
       </c>
       <c r="C77" s="4" t="s">
@@ -2834,10 +3797,10 @@
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78">
+      <c r="A78" s="0">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" t="s" s="0">
         <v>82</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -2845,10 +3808,10 @@
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79">
+      <c r="A79" s="0">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" t="s" s="0">
         <v>83</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -2856,10 +3819,10 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80">
+      <c r="A80" s="0">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" t="s" s="0">
         <v>84</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -2867,10 +3830,10 @@
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81">
+      <c r="A81" s="0">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" t="s" s="0">
         <v>85</v>
       </c>
       <c r="C81" s="2" t="s">
@@ -2878,10 +3841,10 @@
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82">
+      <c r="A82" s="0">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" t="s" s="0">
         <v>86</v>
       </c>
       <c r="C82" s="2" t="s">
@@ -2889,10 +3852,10 @@
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83">
+      <c r="A83" s="0">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" t="s" s="0">
         <v>87</v>
       </c>
       <c r="C83" s="2" t="s">
@@ -2900,10 +3863,10 @@
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84">
+      <c r="A84" s="0">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" t="s" s="0">
         <v>88</v>
       </c>
       <c r="C84" s="2" t="s">
@@ -2911,10 +3874,10 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85">
+      <c r="A85" s="0">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" t="s" s="0">
         <v>89</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -2922,10 +3885,10 @@
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86">
+      <c r="A86" s="0">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" t="s" s="0">
         <v>90</v>
       </c>
       <c r="C86" s="2" t="s">
@@ -2933,10 +3896,10 @@
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87">
+      <c r="A87" s="0">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" t="s" s="0">
         <v>91</v>
       </c>
       <c r="C87" s="2" t="s">
@@ -2944,10 +3907,10 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88">
+      <c r="A88" s="0">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" t="s" s="0">
         <v>92</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -2955,10 +3918,10 @@
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89">
+      <c r="A89" s="0">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" t="s" s="0">
         <v>93</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -2966,10 +3929,10 @@
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90">
+      <c r="A90" s="0">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" t="s" s="0">
         <v>94</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -2977,10 +3940,10 @@
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91">
+      <c r="A91" s="0">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" t="s" s="0">
         <v>95</v>
       </c>
       <c r="C91" s="4" t="s">
@@ -2988,10 +3951,10 @@
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92">
+      <c r="A92" s="0">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" t="s" s="0">
         <v>96</v>
       </c>
       <c r="C92" s="4" t="s">
@@ -2999,10 +3962,10 @@
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93">
+      <c r="A93" s="0">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" t="s" s="0">
         <v>97</v>
       </c>
       <c r="C93" s="2" t="s">
@@ -3010,10 +3973,10 @@
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94">
+      <c r="A94" s="0">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" t="s" s="0">
         <v>98</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -3021,10 +3984,10 @@
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95">
+      <c r="A95" s="0">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" t="s" s="0">
         <v>99</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -3032,10 +3995,10 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96">
+      <c r="A96" s="0">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" t="s" s="0">
         <v>100</v>
       </c>
       <c r="C96" s="2" t="s">
@@ -3043,10 +4006,10 @@
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97">
+      <c r="A97" s="0">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" t="s" s="0">
         <v>101</v>
       </c>
       <c r="C97" s="2" t="s">
@@ -3054,10 +4017,10 @@
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98">
+      <c r="A98" s="0">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" t="s" s="0">
         <v>102</v>
       </c>
       <c r="C98" s="2" t="s">
@@ -3065,10 +4028,10 @@
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99">
+      <c r="A99" s="0">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" t="s" s="0">
         <v>103</v>
       </c>
       <c r="C99" s="2" t="s">
@@ -3076,10 +4039,10 @@
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100">
+      <c r="A100" s="0">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C100" s="2" t="s">
@@ -3087,10 +4050,10 @@
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101">
+      <c r="A101" s="0">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" t="s" s="0">
         <v>105</v>
       </c>
       <c r="C101" s="2" t="s">
@@ -3098,10 +4061,10 @@
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102">
+      <c r="A102" s="0">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" t="s" s="0">
         <v>106</v>
       </c>
       <c r="C102" s="3" t="s">
@@ -3109,10 +4072,10 @@
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103">
+      <c r="A103" s="0">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" t="s" s="0">
         <v>107</v>
       </c>
       <c r="C103" s="2" t="s">
@@ -3120,10 +4083,10 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104">
+      <c r="A104" s="0">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" t="s" s="0">
         <v>108</v>
       </c>
       <c r="C104" s="2" t="s">
@@ -3131,10 +4094,10 @@
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105">
+      <c r="A105" s="0">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" t="s" s="0">
         <v>109</v>
       </c>
       <c r="C105" s="4" t="s">
@@ -3142,10 +4105,10 @@
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106">
+      <c r="A106" s="0">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" t="s" s="0">
         <v>110</v>
       </c>
       <c r="C106" s="2" t="s">
@@ -3153,10 +4116,10 @@
       </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107">
+      <c r="A107" s="0">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" t="s" s="0">
         <v>111</v>
       </c>
       <c r="C107" s="4" t="s">
@@ -3164,10 +4127,10 @@
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108">
+      <c r="A108" s="0">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" t="s" s="0">
         <v>112</v>
       </c>
       <c r="C108" s="2" t="s">
@@ -3175,10 +4138,10 @@
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109">
+      <c r="A109" s="0">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" t="s" s="0">
         <v>113</v>
       </c>
       <c r="C109" s="3" t="s">
@@ -3186,10 +4149,10 @@
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110">
+      <c r="A110" s="0">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" t="s" s="0">
         <v>114</v>
       </c>
       <c r="C110" s="2" t="s">
@@ -3197,10 +4160,10 @@
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111">
+      <c r="A111" s="0">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" t="s" s="0">
         <v>115</v>
       </c>
       <c r="C111" s="2" t="s">
@@ -3208,10 +4171,10 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112">
+      <c r="A112" s="0">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" t="s" s="0">
         <v>116</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -3219,10 +4182,10 @@
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113">
+      <c r="A113" s="0">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" t="s" s="0">
         <v>117</v>
       </c>
       <c r="C113" s="3" t="s">
@@ -3230,10 +4193,10 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114">
+      <c r="A114" s="0">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" t="s" s="0">
         <v>118</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -3241,10 +4204,10 @@
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115">
+      <c r="A115" s="0">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" t="s" s="0">
         <v>119</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -3252,10 +4215,10 @@
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116">
+      <c r="A116" s="0">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" t="s" s="0">
         <v>120</v>
       </c>
       <c r="C116" s="2" t="s">
@@ -3263,10 +4226,10 @@
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117">
+      <c r="A117" s="0">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" t="s" s="0">
         <v>121</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -3274,10 +4237,10 @@
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118">
+      <c r="A118" s="0">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" t="s" s="0">
         <v>122</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -3285,10 +4248,10 @@
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119">
+      <c r="A119" s="0">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" t="s" s="0">
         <v>123</v>
       </c>
       <c r="C119" s="2" t="s">
@@ -3296,10 +4259,10 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120">
+      <c r="A120" s="0">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" t="s" s="0">
         <v>124</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -3307,10 +4270,10 @@
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121">
+      <c r="A121" s="0">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" t="s" s="0">
         <v>125</v>
       </c>
       <c r="C121" s="2" t="s">
@@ -3318,10 +4281,10 @@
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122">
+      <c r="A122" s="0">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" t="s" s="0">
         <v>126</v>
       </c>
       <c r="C122" s="2" t="s">
@@ -3329,10 +4292,10 @@
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123">
+      <c r="A123" s="0">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" t="s" s="0">
         <v>127</v>
       </c>
       <c r="C123" s="2" t="s">
@@ -3340,10 +4303,10 @@
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124">
+      <c r="A124" s="0">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" t="s" s="0">
         <v>128</v>
       </c>
       <c r="C124" s="2" t="s">
@@ -3351,10 +4314,10 @@
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125">
+      <c r="A125" s="0">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" t="s" s="0">
         <v>129</v>
       </c>
       <c r="C125" s="2" t="s">
@@ -3362,10 +4325,10 @@
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126">
+      <c r="A126" s="0">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" t="s" s="0">
         <v>130</v>
       </c>
       <c r="C126" s="2" t="s">
@@ -3373,10 +4336,10 @@
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127">
+      <c r="A127" s="0">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" t="s" s="0">
         <v>131</v>
       </c>
       <c r="C127" s="2" t="s">
@@ -3384,10 +4347,10 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128">
+      <c r="A128" s="0">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" t="s" s="0">
         <v>132</v>
       </c>
       <c r="C128" s="2" t="s">
@@ -3395,10 +4358,10 @@
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129">
+      <c r="A129" s="0">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" t="s" s="0">
         <v>133</v>
       </c>
       <c r="C129" s="2" t="s">
@@ -3406,10 +4369,10 @@
       </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130">
+      <c r="A130" s="0">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" t="s" s="0">
         <v>134</v>
       </c>
       <c r="C130" s="4" t="s">
@@ -3417,10 +4380,10 @@
       </c>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131">
+      <c r="A131" s="0">
         <v>130</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" t="s" s="0">
         <v>135</v>
       </c>
       <c r="C131" s="2" t="s">
@@ -3428,10 +4391,10 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132">
+      <c r="A132" s="0">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" t="s" s="0">
         <v>136</v>
       </c>
       <c r="C132" s="4" t="s">
@@ -3439,10 +4402,10 @@
       </c>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133">
+      <c r="A133" s="0">
         <v>132</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" t="s" s="0">
         <v>137</v>
       </c>
       <c r="C133" s="2" t="s">
@@ -3450,10 +4413,10 @@
       </c>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134">
+      <c r="A134" s="0">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" t="s" s="0">
         <v>138</v>
       </c>
       <c r="C134" s="2" t="s">
@@ -3461,10 +4424,10 @@
       </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135">
+      <c r="A135" s="0">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" t="s" s="0">
         <v>139</v>
       </c>
       <c r="C135" s="2" t="s">
@@ -3472,10 +4435,10 @@
       </c>
     </row>
     <row r="136" spans="1:3">
-      <c r="A136">
+      <c r="A136" s="0">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" t="s" s="0">
         <v>140</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -3483,10 +4446,10 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137">
+      <c r="A137" s="0">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" t="s" s="0">
         <v>141</v>
       </c>
       <c r="C137" s="2" t="s">
@@ -3494,10 +4457,10 @@
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138">
+      <c r="A138" s="0">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" t="s" s="0">
         <v>142</v>
       </c>
       <c r="C138" s="2" t="s">
@@ -3505,10 +4468,10 @@
       </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139">
+      <c r="A139" s="0">
         <v>138</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" t="s" s="0">
         <v>143</v>
       </c>
       <c r="C139" s="2" t="s">
@@ -3516,10 +4479,10 @@
       </c>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140">
+      <c r="A140" s="0">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" t="s" s="0">
         <v>144</v>
       </c>
       <c r="C140" s="3" t="s">
@@ -3527,10 +4490,10 @@
       </c>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141">
+      <c r="A141" s="0">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" t="s" s="0">
         <v>145</v>
       </c>
       <c r="C141" s="4" t="s">
@@ -3538,10 +4501,10 @@
       </c>
     </row>
     <row r="142" spans="1:3">
-      <c r="A142">
+      <c r="A142" s="0">
         <v>141</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" t="s" s="0">
         <v>146</v>
       </c>
       <c r="C142" s="2" t="s">
@@ -3549,10 +4512,10 @@
       </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143">
+      <c r="A143" s="0">
         <v>142</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" t="s" s="0">
         <v>147</v>
       </c>
       <c r="C143" s="3" t="s">
@@ -3560,10 +4523,10 @@
       </c>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144">
+      <c r="A144" s="0">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" t="s" s="0">
         <v>148</v>
       </c>
       <c r="C144" s="4" t="s">
@@ -3571,10 +4534,10 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145">
+      <c r="A145" s="0">
         <v>144</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" t="s" s="0">
         <v>149</v>
       </c>
       <c r="C145" s="2" t="s">
@@ -3582,10 +4545,10 @@
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146">
+      <c r="A146" s="0">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" t="s" s="0">
         <v>150</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -3593,10 +4556,10 @@
       </c>
     </row>
     <row r="147" spans="1:3">
-      <c r="A147">
+      <c r="A147" s="0">
         <v>146</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" t="s" s="0">
         <v>151</v>
       </c>
       <c r="C147" s="2" t="s">
@@ -3604,10 +4567,10 @@
       </c>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148">
+      <c r="A148" s="0">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" t="s" s="0">
         <v>152</v>
       </c>
       <c r="C148" s="2" t="s">
@@ -3615,10 +4578,10 @@
       </c>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149">
+      <c r="A149" s="0">
         <v>148</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" t="s" s="0">
         <v>153</v>
       </c>
       <c r="C149" s="2" t="s">
@@ -3626,10 +4589,10 @@
       </c>
     </row>
     <row r="150" spans="1:3">
-      <c r="A150">
+      <c r="A150" s="0">
         <v>149</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" t="s" s="0">
         <v>154</v>
       </c>
       <c r="C150" s="2" t="s">
@@ -3637,10 +4600,10 @@
       </c>
     </row>
     <row r="151" spans="1:3">
-      <c r="A151">
+      <c r="A151" s="0">
         <v>150</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" t="s" s="0">
         <v>155</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -3648,10 +4611,10 @@
       </c>
     </row>
     <row r="152" spans="1:3">
-      <c r="A152">
+      <c r="A152" s="0">
         <v>151</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" t="s" s="0">
         <v>156</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -3659,10 +4622,10 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153">
+      <c r="A153" s="0">
         <v>152</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" t="s" s="0">
         <v>157</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -3670,10 +4633,10 @@
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154">
+      <c r="A154" s="0">
         <v>153</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" t="s" s="0">
         <v>158</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -3681,10 +4644,10 @@
       </c>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155">
+      <c r="A155" s="0">
         <v>154</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" t="s" s="0">
         <v>159</v>
       </c>
       <c r="C155" s="2" t="s">
@@ -3692,10 +4655,10 @@
       </c>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156">
+      <c r="A156" s="0">
         <v>155</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" t="s" s="0">
         <v>160</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -3703,10 +4666,10 @@
       </c>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157">
+      <c r="A157" s="0">
         <v>156</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" t="s" s="0">
         <v>161</v>
       </c>
       <c r="C157" s="4" t="s">
@@ -3714,10 +4677,10 @@
       </c>
     </row>
     <row r="158" spans="1:3">
-      <c r="A158">
+      <c r="A158" s="0">
         <v>157</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" t="s" s="0">
         <v>162</v>
       </c>
       <c r="C158" s="2" t="s">
@@ -3725,10 +4688,10 @@
       </c>
     </row>
     <row r="159" spans="1:3">
-      <c r="A159">
+      <c r="A159" s="0">
         <v>158</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" t="s" s="0">
         <v>163</v>
       </c>
       <c r="C159" s="2" t="s">
@@ -3736,10 +4699,10 @@
       </c>
     </row>
     <row r="160" spans="1:3">
-      <c r="A160">
+      <c r="A160" s="0">
         <v>159</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" t="s" s="0">
         <v>164</v>
       </c>
       <c r="C160" s="2" t="s">
@@ -3747,10 +4710,10 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161">
+      <c r="A161" s="0">
         <v>160</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" t="s" s="0">
         <v>165</v>
       </c>
       <c r="C161" s="2" t="s">
@@ -3758,10 +4721,10 @@
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162">
+      <c r="A162" s="0">
         <v>161</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" t="s" s="0">
         <v>166</v>
       </c>
       <c r="C162" s="4" t="s">
@@ -3769,10 +4732,10 @@
       </c>
     </row>
     <row r="163" spans="1:3">
-      <c r="A163">
+      <c r="A163" s="0">
         <v>162</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" t="s" s="0">
         <v>167</v>
       </c>
       <c r="C163" s="3" t="s">
@@ -3780,10 +4743,10 @@
       </c>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164">
+      <c r="A164" s="0">
         <v>163</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" t="s" s="0">
         <v>168</v>
       </c>
       <c r="C164" s="2" t="s">
@@ -3791,10 +4754,10 @@
       </c>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165">
+      <c r="A165" s="0">
         <v>164</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" t="s" s="0">
         <v>169</v>
       </c>
       <c r="C165" s="2" t="s">
@@ -3802,10 +4765,10 @@
       </c>
     </row>
     <row r="166" spans="1:3">
-      <c r="A166">
+      <c r="A166" s="0">
         <v>165</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" t="s" s="0">
         <v>170</v>
       </c>
       <c r="C166" s="2" t="s">
@@ -3813,10 +4776,10 @@
       </c>
     </row>
     <row r="167" spans="1:3">
-      <c r="A167">
+      <c r="A167" s="0">
         <v>166</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" t="s" s="0">
         <v>171</v>
       </c>
       <c r="C167" s="2" t="s">
@@ -3824,10 +4787,10 @@
       </c>
     </row>
     <row r="168" spans="1:3">
-      <c r="A168">
+      <c r="A168" s="0">
         <v>167</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" t="s" s="0">
         <v>172</v>
       </c>
       <c r="C168" s="2" t="s">
@@ -3835,10 +4798,10 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169">
+      <c r="A169" s="0">
         <v>168</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" t="s" s="0">
         <v>173</v>
       </c>
       <c r="C169" s="2" t="s">
@@ -3846,10 +4809,10 @@
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170">
+      <c r="A170" s="0">
         <v>169</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" t="s" s="0">
         <v>174</v>
       </c>
       <c r="C170" s="2" t="s">
@@ -3857,10 +4820,10 @@
       </c>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171">
+      <c r="A171" s="0">
         <v>170</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" t="s" s="0">
         <v>175</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -3868,10 +4831,10 @@
       </c>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172">
+      <c r="A172" s="0">
         <v>171</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" t="s" s="0">
         <v>176</v>
       </c>
       <c r="C172" s="2" t="s">
@@ -3879,10 +4842,10 @@
       </c>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173">
+      <c r="A173" s="0">
         <v>172</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" t="s" s="0">
         <v>177</v>
       </c>
       <c r="C173" s="4" t="s">
@@ -3890,10 +4853,10 @@
       </c>
     </row>
     <row r="174" spans="1:3">
-      <c r="A174">
+      <c r="A174" s="0">
         <v>173</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" t="s" s="0">
         <v>178</v>
       </c>
       <c r="C174" s="3" t="s">
@@ -3901,10 +4864,10 @@
       </c>
     </row>
     <row r="175" spans="1:3">
-      <c r="A175">
+      <c r="A175" s="0">
         <v>174</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" t="s" s="0">
         <v>179</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -3912,10 +4875,10 @@
       </c>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176">
+      <c r="A176" s="0">
         <v>175</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" t="s" s="0">
         <v>180</v>
       </c>
       <c r="C176" s="3" t="s">
@@ -3923,10 +4886,10 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177">
+      <c r="A177" s="0">
         <v>176</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" t="s" s="0">
         <v>181</v>
       </c>
       <c r="C177" s="2" t="s">
@@ -3934,10 +4897,10 @@
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178">
+      <c r="A178" s="0">
         <v>177</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" t="s" s="0">
         <v>182</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -3945,10 +4908,10 @@
       </c>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179">
+      <c r="A179" s="0">
         <v>178</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" t="s" s="0">
         <v>183</v>
       </c>
       <c r="C179" s="2" t="s">
@@ -3956,10 +4919,10 @@
       </c>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180">
+      <c r="A180" s="0">
         <v>179</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" t="s" s="0">
         <v>184</v>
       </c>
       <c r="C180" s="2" t="s">
@@ -3967,10 +4930,10 @@
       </c>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181">
+      <c r="A181" s="0">
         <v>180</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C181" s="3" t="s">
@@ -3978,10 +4941,10 @@
       </c>
     </row>
     <row r="182" spans="1:3">
-      <c r="A182">
+      <c r="A182" s="0">
         <v>181</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" t="s" s="0">
         <v>186</v>
       </c>
       <c r="C182" s="2" t="s">
@@ -3989,10 +4952,10 @@
       </c>
     </row>
     <row r="183" spans="1:3">
-      <c r="A183">
+      <c r="A183" s="0">
         <v>182</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" t="s" s="0">
         <v>187</v>
       </c>
       <c r="C183" s="4" t="s">
@@ -4000,10 +4963,10 @@
       </c>
     </row>
     <row r="184" spans="1:3">
-      <c r="A184">
+      <c r="A184" s="0">
         <v>183</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" t="s" s="0">
         <v>188</v>
       </c>
       <c r="C184" s="2" t="s">
@@ -4011,10 +4974,10 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185">
+      <c r="A185" s="0">
         <v>184</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" t="s" s="0">
         <v>189</v>
       </c>
       <c r="C185" s="4" t="s">
@@ -4022,10 +4985,10 @@
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186">
+      <c r="A186" s="0">
         <v>185</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" t="s" s="0">
         <v>190</v>
       </c>
       <c r="C186" s="2" t="s">
@@ -4033,10 +4996,10 @@
       </c>
     </row>
     <row r="187" spans="1:3">
-      <c r="A187">
+      <c r="A187" s="0">
         <v>186</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" t="s" s="0">
         <v>191</v>
       </c>
       <c r="C187" s="2" t="s">
@@ -4044,10 +5007,10 @@
       </c>
     </row>
     <row r="188" spans="1:3">
-      <c r="A188">
+      <c r="A188" s="0">
         <v>187</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" t="s" s="0">
         <v>192</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -4055,10 +5018,10 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189">
+      <c r="A189" s="0">
         <v>188</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" t="s" s="0">
         <v>193</v>
       </c>
       <c r="C189" s="2" t="s">
@@ -4066,10 +5029,10 @@
       </c>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190">
+      <c r="A190" s="0">
         <v>189</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" t="s" s="0">
         <v>194</v>
       </c>
       <c r="C190" s="2" t="s">
@@ -4077,10 +5040,10 @@
       </c>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191">
+      <c r="A191" s="0">
         <v>190</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" t="s" s="0">
         <v>195</v>
       </c>
       <c r="C191" s="2" t="s">
@@ -4088,10 +5051,10 @@
       </c>
     </row>
     <row r="192" spans="1:3">
-      <c r="A192">
+      <c r="A192" s="0">
         <v>191</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" t="s" s="0">
         <v>196</v>
       </c>
       <c r="C192" s="2" t="s">
@@ -4099,10 +5062,10 @@
       </c>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193">
+      <c r="A193" s="0">
         <v>192</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" t="s" s="0">
         <v>197</v>
       </c>
       <c r="C193" s="2" t="s">
@@ -4110,10 +5073,10 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194">
+      <c r="A194" s="0">
         <v>193</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" t="s" s="0">
         <v>198</v>
       </c>
       <c r="C194" s="4" t="s">
@@ -4121,10 +5084,10 @@
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195">
+      <c r="A195" s="0">
         <v>194</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" t="s" s="0">
         <v>199</v>
       </c>
       <c r="C195" s="4" t="s">
@@ -4132,10 +5095,10 @@
       </c>
     </row>
     <row r="196" spans="1:3">
-      <c r="A196">
+      <c r="A196" s="0">
         <v>195</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" t="s" s="0">
         <v>200</v>
       </c>
       <c r="C196" s="2" t="s">
@@ -4143,10 +5106,10 @@
       </c>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197">
+      <c r="A197" s="0">
         <v>196</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C197" s="2" t="s">
@@ -4154,10 +5117,10 @@
       </c>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198">
+      <c r="A198" s="0">
         <v>197</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" t="s" s="0">
         <v>202</v>
       </c>
       <c r="C198" s="2" t="s">
@@ -4165,10 +5128,10 @@
       </c>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199">
+      <c r="A199" s="0">
         <v>198</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" t="s" s="0">
         <v>203</v>
       </c>
       <c r="C199" s="4" t="s">
@@ -4176,10 +5139,10 @@
       </c>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200">
+      <c r="A200" s="0">
         <v>199</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" t="s" s="0">
         <v>204</v>
       </c>
       <c r="C200" s="2" t="s">
@@ -4187,10 +5150,10 @@
       </c>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201">
+      <c r="A201" s="0">
         <v>200</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" t="s" s="0">
         <v>205</v>
       </c>
       <c r="C201" s="2" t="s">
@@ -4198,10 +5161,10 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202">
+      <c r="A202" s="0">
         <v>201</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" t="s" s="0">
         <v>206</v>
       </c>
       <c r="C202" s="4" t="s">
@@ -4209,10 +5172,10 @@
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203">
+      <c r="A203" s="0">
         <v>202</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" t="s" s="0">
         <v>207</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -4220,10 +5183,10 @@
       </c>
     </row>
     <row r="204" spans="1:3">
-      <c r="A204">
+      <c r="A204" s="0">
         <v>203</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" t="s" s="0">
         <v>208</v>
       </c>
       <c r="C204" s="2" t="s">
@@ -4231,10 +5194,10 @@
       </c>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205">
+      <c r="A205" s="0">
         <v>204</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" t="s" s="0">
         <v>209</v>
       </c>
       <c r="C205" s="2" t="s">
@@ -4242,10 +5205,10 @@
       </c>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206">
+      <c r="A206" s="0">
         <v>205</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" t="s" s="0">
         <v>210</v>
       </c>
       <c r="C206" s="2" t="s">
@@ -4253,10 +5216,10 @@
       </c>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207">
+      <c r="A207" s="0">
         <v>206</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" t="s" s="0">
         <v>211</v>
       </c>
       <c r="C207" s="2" t="s">
@@ -4264,10 +5227,10 @@
       </c>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208">
+      <c r="A208" s="0">
         <v>207</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" t="s" s="0">
         <v>212</v>
       </c>
       <c r="C208" s="2" t="s">
@@ -4275,10 +5238,10 @@
       </c>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209">
+      <c r="A209" s="0">
         <v>208</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" t="s" s="0">
         <v>213</v>
       </c>
       <c r="C209" s="2" t="s">
@@ -4286,10 +5249,10 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210">
+      <c r="A210" s="0">
         <v>209</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" t="s" s="0">
         <v>214</v>
       </c>
       <c r="C210" s="2" t="s">
@@ -4297,10 +5260,10 @@
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211">
+      <c r="A211" s="0">
         <v>210</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" t="s" s="0">
         <v>215</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -4308,10 +5271,10 @@
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212">
+      <c r="A212" s="0">
         <v>211</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" t="s" s="0">
         <v>216</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -4319,10 +5282,10 @@
       </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213">
+      <c r="A213" s="0">
         <v>212</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" t="s" s="0">
         <v>217</v>
       </c>
       <c r="C213" s="2" t="s">
@@ -4330,10 +5293,10 @@
       </c>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214">
+      <c r="A214" s="0">
         <v>213</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" t="s" s="0">
         <v>218</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -4341,10 +5304,10 @@
       </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215">
+      <c r="A215" s="0">
         <v>214</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" t="s" s="0">
         <v>219</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -4352,10 +5315,10 @@
       </c>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216">
+      <c r="A216" s="0">
         <v>215</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" t="s" s="0">
         <v>220</v>
       </c>
       <c r="C216" s="2" t="s">
@@ -4363,10 +5326,10 @@
       </c>
     </row>
     <row r="217" spans="1:3">
-      <c r="A217">
+      <c r="A217" s="0">
         <v>216</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" t="s" s="0">
         <v>221</v>
       </c>
       <c r="C217" s="2" t="s">
@@ -4374,10 +5337,10 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218">
+      <c r="A218" s="0">
         <v>217</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" t="s" s="0">
         <v>222</v>
       </c>
       <c r="C218" s="4" t="s">
@@ -4385,10 +5348,10 @@
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219">
+      <c r="A219" s="0">
         <v>218</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" t="s" s="0">
         <v>223</v>
       </c>
       <c r="C219" s="4" t="s">
@@ -4396,10 +5359,10 @@
       </c>
     </row>
     <row r="220" spans="1:3">
-      <c r="A220">
+      <c r="A220" s="0">
         <v>219</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" t="s" s="0">
         <v>224</v>
       </c>
       <c r="C220" s="3" t="s">
@@ -4407,10 +5370,10 @@
       </c>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221">
+      <c r="A221" s="0">
         <v>220</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C221" s="3" t="s">
@@ -4418,10 +5381,10 @@
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222">
+      <c r="A222" s="0">
         <v>221</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" t="s" s="0">
         <v>226</v>
       </c>
       <c r="C222" s="2" t="s">
@@ -4429,10 +5392,10 @@
       </c>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223">
+      <c r="A223" s="0">
         <v>222</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" t="s" s="0">
         <v>227</v>
       </c>
       <c r="C223" s="4" t="s">
@@ -4440,10 +5403,10 @@
       </c>
     </row>
     <row r="224" spans="1:3">
-      <c r="A224">
+      <c r="A224" s="0">
         <v>223</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" t="s" s="0">
         <v>228</v>
       </c>
       <c r="C224" s="2" t="s">
@@ -4451,10 +5414,10 @@
       </c>
     </row>
     <row r="225" spans="1:3">
-      <c r="A225">
+      <c r="A225" s="0">
         <v>224</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C225" s="2" t="s">
@@ -4462,10 +5425,10 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226">
+      <c r="A226" s="0">
         <v>225</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" t="s" s="0">
         <v>230</v>
       </c>
       <c r="C226" s="3" t="s">
@@ -4473,10 +5436,10 @@
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227">
+      <c r="A227" s="0">
         <v>226</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" t="s" s="0">
         <v>231</v>
       </c>
       <c r="C227" s="2" t="s">
@@ -4484,10 +5447,10 @@
       </c>
     </row>
     <row r="228" spans="1:3">
-      <c r="A228">
+      <c r="A228" s="0">
         <v>227</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" t="s" s="0">
         <v>232</v>
       </c>
       <c r="C228" s="2" t="s">
@@ -4495,10 +5458,10 @@
       </c>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229">
+      <c r="A229" s="0">
         <v>228</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C229" s="3" t="s">
@@ -4506,10 +5469,10 @@
       </c>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230">
+      <c r="A230" s="0">
         <v>229</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" t="s" s="0">
         <v>234</v>
       </c>
       <c r="C230" s="2" t="s">
@@ -4517,10 +5480,10 @@
       </c>
     </row>
     <row r="231" spans="1:3">
-      <c r="A231">
+      <c r="A231" s="0">
         <v>230</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" t="s" s="0">
         <v>235</v>
       </c>
       <c r="C231" s="2" t="s">
@@ -4528,10 +5491,10 @@
       </c>
     </row>
     <row r="232" spans="1:3">
-      <c r="A232">
+      <c r="A232" s="0">
         <v>231</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" t="s" s="0">
         <v>236</v>
       </c>
       <c r="C232" s="2" t="s">
@@ -4539,10 +5502,10 @@
       </c>
     </row>
     <row r="233" spans="1:3">
-      <c r="A233">
+      <c r="A233" s="0">
         <v>232</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C233" s="2" t="s">
@@ -4550,10 +5513,10 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234">
+      <c r="A234" s="0">
         <v>233</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" t="s" s="0">
         <v>238</v>
       </c>
       <c r="C234" s="2" t="s">
@@ -4561,10 +5524,10 @@
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235">
+      <c r="A235" s="0">
         <v>234</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" t="s" s="0">
         <v>239</v>
       </c>
       <c r="C235" s="4" t="s">
@@ -4572,10 +5535,10 @@
       </c>
     </row>
     <row r="236" spans="1:3">
-      <c r="A236">
+      <c r="A236" s="0">
         <v>235</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" t="s" s="0">
         <v>240</v>
       </c>
       <c r="C236" s="3" t="s">
@@ -4583,10 +5546,10 @@
       </c>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237">
+      <c r="A237" s="0">
         <v>236</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" t="s" s="0">
         <v>241</v>
       </c>
       <c r="C237" s="2" t="s">
@@ -4594,10 +5557,10 @@
       </c>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238">
+      <c r="A238" s="0">
         <v>237</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" t="s" s="0">
         <v>242</v>
       </c>
       <c r="C238" s="2" t="s">
@@ -4605,10 +5568,10 @@
       </c>
     </row>
     <row r="239" spans="1:3">
-      <c r="A239">
+      <c r="A239" s="0">
         <v>238</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" t="s" s="0">
         <v>243</v>
       </c>
       <c r="C239" s="2" t="s">
@@ -4616,10 +5579,10 @@
       </c>
     </row>
     <row r="240" spans="1:3">
-      <c r="A240">
+      <c r="A240" s="0">
         <v>239</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" t="s" s="0">
         <v>244</v>
       </c>
       <c r="C240" s="2" t="s">
@@ -4627,10 +5590,10 @@
       </c>
     </row>
     <row r="241" spans="1:3">
-      <c r="A241">
+      <c r="A241" s="0">
         <v>240</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C241" s="3" t="s">
@@ -4638,10 +5601,10 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242">
+      <c r="A242" s="0">
         <v>241</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" t="s" s="0">
         <v>246</v>
       </c>
       <c r="C242" s="2" t="s">
@@ -4649,10 +5612,10 @@
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243">
+      <c r="A243" s="0">
         <v>242</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" t="s" s="0">
         <v>247</v>
       </c>
       <c r="C243" s="2" t="s">
@@ -4660,10 +5623,10 @@
       </c>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244">
+      <c r="A244" s="0">
         <v>243</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" t="s" s="0">
         <v>248</v>
       </c>
       <c r="C244" s="2" t="s">
@@ -4671,10 +5634,10 @@
       </c>
     </row>
     <row r="245" spans="1:3">
-      <c r="A245">
+      <c r="A245" s="0">
         <v>244</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C245" s="4" t="s">
@@ -4682,10 +5645,10 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246">
+      <c r="A246" s="0">
         <v>245</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" t="s" s="0">
         <v>250</v>
       </c>
       <c r="C246" s="2" t="s">
@@ -4693,10 +5656,10 @@
       </c>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247">
+      <c r="A247" s="0">
         <v>246</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" t="s" s="0">
         <v>251</v>
       </c>
       <c r="C247" s="2" t="s">
@@ -4704,10 +5667,10 @@
       </c>
     </row>
     <row r="248" spans="1:3">
-      <c r="A248">
+      <c r="A248" s="0">
         <v>247</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" t="s" s="0">
         <v>252</v>
       </c>
       <c r="C248" s="2" t="s">
@@ -4715,10 +5678,10 @@
       </c>
     </row>
     <row r="249" spans="1:3">
-      <c r="A249">
+      <c r="A249" s="0">
         <v>248</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C249" s="2" t="s">
@@ -4726,10 +5689,10 @@
       </c>
     </row>
     <row r="250" spans="1:3">
-      <c r="A250">
+      <c r="A250" s="0">
         <v>249</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" t="s" s="0">
         <v>254</v>
       </c>
       <c r="C250" s="2" t="s">
@@ -4737,10 +5700,10 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251">
+      <c r="A251" s="0">
         <v>250</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" t="s" s="0">
         <v>255</v>
       </c>
       <c r="C251" s="3" t="s">
@@ -4748,10 +5711,10 @@
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252">
+      <c r="A252" s="0">
         <v>251</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" t="s" s="0">
         <v>256</v>
       </c>
       <c r="C252" s="2" t="s">
@@ -4759,10 +5722,10 @@
       </c>
     </row>
     <row r="253" spans="1:3">
-      <c r="A253">
+      <c r="A253" s="0">
         <v>252</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C253" s="2" t="s">
@@ -4770,10 +5733,10 @@
       </c>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254">
+      <c r="A254" s="0">
         <v>253</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" t="s" s="0">
         <v>258</v>
       </c>
       <c r="C254" s="2" t="s">
@@ -4781,10 +5744,10 @@
       </c>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255">
+      <c r="A255" s="0">
         <v>254</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" t="s" s="0">
         <v>259</v>
       </c>
       <c r="C255" s="2" t="s">
@@ -4792,10 +5755,10 @@
       </c>
     </row>
     <row r="256" spans="1:3">
-      <c r="A256">
+      <c r="A256" s="0">
         <v>255</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" t="s" s="0">
         <v>260</v>
       </c>
       <c r="C256" s="2" t="s">
@@ -4803,10 +5766,10 @@
       </c>
     </row>
     <row r="257" spans="1:3">
-      <c r="A257">
+      <c r="A257" s="0">
         <v>256</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C257" s="2" t="s">
@@ -4814,10 +5777,10 @@
       </c>
     </row>
     <row r="258" spans="1:3">
-      <c r="A258">
+      <c r="A258" s="0">
         <v>257</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" t="s" s="0">
         <v>262</v>
       </c>
       <c r="C258" s="4" t="s">
@@ -4825,10 +5788,10 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259">
+      <c r="A259" s="0">
         <v>258</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" t="s" s="0">
         <v>263</v>
       </c>
       <c r="C259" s="2" t="s">
@@ -4836,10 +5799,10 @@
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260">
+      <c r="A260" s="0">
         <v>259</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" t="s" s="0">
         <v>264</v>
       </c>
       <c r="C260" s="4" t="s">
@@ -4847,10 +5810,10 @@
       </c>
     </row>
     <row r="261" spans="1:3">
-      <c r="A261">
+      <c r="A261" s="0">
         <v>260</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C261" s="2" t="s">
@@ -4858,10 +5821,10 @@
       </c>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262">
+      <c r="A262" s="0">
         <v>261</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" t="s" s="0">
         <v>266</v>
       </c>
       <c r="C262" s="2" t="s">
@@ -4869,10 +5832,10 @@
       </c>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263">
+      <c r="A263" s="0">
         <v>262</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" t="s" s="0">
         <v>267</v>
       </c>
       <c r="C263" s="2" t="s">
@@ -4880,10 +5843,10 @@
       </c>
     </row>
     <row r="264" spans="1:3">
-      <c r="A264">
+      <c r="A264" s="0">
         <v>263</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" t="s" s="0">
         <v>268</v>
       </c>
       <c r="C264" s="2" t="s">
@@ -4891,10 +5854,10 @@
       </c>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265">
+      <c r="A265" s="0">
         <v>264</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C265" s="3" t="s">
@@ -4902,10 +5865,10 @@
       </c>
     </row>
     <row r="266" spans="1:3">
-      <c r="A266">
+      <c r="A266" s="0">
         <v>265</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" t="s" s="0">
         <v>270</v>
       </c>
       <c r="C266" s="3" t="s">
@@ -4913,10 +5876,10 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267">
+      <c r="A267" s="0">
         <v>266</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C267" s="2" t="s">
@@ -4924,10 +5887,10 @@
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268">
+      <c r="A268" s="0">
         <v>267</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" t="s" s="0">
         <v>272</v>
       </c>
       <c r="C268" s="3" t="s">
@@ -4935,10 +5898,10 @@
       </c>
     </row>
     <row r="269" spans="1:3">
-      <c r="A269">
+      <c r="A269" s="0">
         <v>268</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C269" s="2" t="s">
@@ -4946,10 +5909,10 @@
       </c>
     </row>
     <row r="270" spans="1:3">
-      <c r="A270">
+      <c r="A270" s="0">
         <v>269</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" t="s" s="0">
         <v>274</v>
       </c>
       <c r="C270" s="2" t="s">
@@ -4957,10 +5920,10 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271">
+      <c r="A271" s="0">
         <v>270</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C271" s="2" t="s">
@@ -4968,10 +5931,10 @@
       </c>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272">
+      <c r="A272" s="0">
         <v>271</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" t="s" s="0">
         <v>276</v>
       </c>
       <c r="C272" s="2" t="s">
@@ -4979,10 +5942,10 @@
       </c>
     </row>
     <row r="273" spans="1:3">
-      <c r="A273">
+      <c r="A273" s="0">
         <v>272</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -4990,10 +5953,10 @@
       </c>
     </row>
     <row r="274" spans="1:3">
-      <c r="A274">
+      <c r="A274" s="0">
         <v>273</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" t="s" s="0">
         <v>278</v>
       </c>
       <c r="C274" s="2" t="s">
@@ -5001,10 +5964,10 @@
       </c>
     </row>
     <row r="275" spans="1:3">
-      <c r="A275">
+      <c r="A275" s="0">
         <v>274</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C275" s="4" t="s">
@@ -5012,10 +5975,10 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276">
+      <c r="A276" s="0">
         <v>275</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" t="s" s="0">
         <v>280</v>
       </c>
       <c r="C276" s="2" t="s">
@@ -5023,10 +5986,10 @@
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277">
+      <c r="A277" s="0">
         <v>276</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C277" s="2" t="s">
@@ -5034,10 +5997,10 @@
       </c>
     </row>
     <row r="278" spans="1:3">
-      <c r="A278">
+      <c r="A278" s="0">
         <v>277</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" t="s" s="0">
         <v>282</v>
       </c>
       <c r="C278" s="2" t="s">
@@ -5045,10 +6008,10 @@
       </c>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279">
+      <c r="A279" s="0">
         <v>278</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" t="s" s="0">
         <v>283</v>
       </c>
       <c r="C279" s="2" t="s">
@@ -5056,10 +6019,10 @@
       </c>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280">
+      <c r="A280" s="0">
         <v>279</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" t="s" s="0">
         <v>284</v>
       </c>
       <c r="C280" s="2" t="s">
@@ -5067,10 +6030,10 @@
       </c>
     </row>
     <row r="281" spans="1:3">
-      <c r="A281">
+      <c r="A281" s="0">
         <v>280</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C281" s="2" t="s">
@@ -5078,10 +6041,10 @@
       </c>
     </row>
     <row r="282" spans="1:3">
-      <c r="A282">
+      <c r="A282" s="0">
         <v>281</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" t="s" s="0">
         <v>286</v>
       </c>
       <c r="C282" s="2" t="s">
@@ -5089,10 +6052,10 @@
       </c>
     </row>
     <row r="283" spans="1:3">
-      <c r="A283">
+      <c r="A283" s="0">
         <v>282</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" t="s" s="0">
         <v>287</v>
       </c>
       <c r="C283" s="4" t="s">
@@ -5100,10 +6063,10 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284">
+      <c r="A284" s="0">
         <v>283</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" t="s" s="0">
         <v>288</v>
       </c>
       <c r="C284" s="4" t="s">
@@ -5111,10 +6074,10 @@
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285">
+      <c r="A285" s="0">
         <v>284</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C285" s="4" t="s">
@@ -5122,10 +6085,10 @@
       </c>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286">
+      <c r="A286" s="0">
         <v>285</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" t="s" s="0">
         <v>290</v>
       </c>
       <c r="C286" s="2" t="s">
@@ -5133,10 +6096,10 @@
       </c>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287">
+      <c r="A287" s="0">
         <v>286</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" t="s" s="0">
         <v>291</v>
       </c>
       <c r="C287" s="2" t="s">
@@ -5144,10 +6107,10 @@
       </c>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288">
+      <c r="A288" s="0">
         <v>287</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" t="s" s="0">
         <v>292</v>
       </c>
       <c r="C288" s="3" t="s">
@@ -5155,10 +6118,10 @@
       </c>
     </row>
     <row r="289" spans="1:3">
-      <c r="A289">
+      <c r="A289" s="0">
         <v>288</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C289" s="3" t="s">
@@ -5166,10 +6129,10 @@
       </c>
     </row>
     <row r="290" spans="1:3">
-      <c r="A290">
+      <c r="A290" s="0">
         <v>289</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" t="s" s="0">
         <v>294</v>
       </c>
       <c r="C290" s="2" t="s">
@@ -5177,10 +6140,10 @@
       </c>
     </row>
     <row r="291" spans="1:3">
-      <c r="A291">
+      <c r="A291" s="0">
         <v>290</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" t="s" s="0">
         <v>295</v>
       </c>
       <c r="C291" s="2" t="s">
@@ -5188,10 +6151,10 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292">
+      <c r="A292" s="0">
         <v>291</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" t="s" s="0">
         <v>296</v>
       </c>
       <c r="C292" s="2" t="s">
@@ -5199,10 +6162,10 @@
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293">
+      <c r="A293" s="0">
         <v>292</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C293" s="2" t="s">
@@ -5210,10 +6173,10 @@
       </c>
     </row>
     <row r="294" spans="1:3">
-      <c r="A294">
+      <c r="A294" s="0">
         <v>293</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B294" t="s" s="0">
         <v>298</v>
       </c>
       <c r="C294" s="2" t="s">
@@ -5221,10 +6184,10 @@
       </c>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295">
+      <c r="A295" s="0">
         <v>294</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B295" t="s" s="0">
         <v>299</v>
       </c>
       <c r="C295" s="2" t="s">
@@ -5232,10 +6195,10 @@
       </c>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296">
+      <c r="A296" s="0">
         <v>295</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B296" t="s" s="0">
         <v>300</v>
       </c>
       <c r="C296" s="4" t="s">
@@ -5243,10 +6206,10 @@
       </c>
     </row>
     <row r="297" spans="1:3">
-      <c r="A297">
+      <c r="A297" s="0">
         <v>296</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B297" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C297" s="2" t="s">
@@ -5254,10 +6217,10 @@
       </c>
     </row>
     <row r="298" spans="1:3">
-      <c r="A298">
+      <c r="A298" s="0">
         <v>297</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B298" t="s" s="0">
         <v>302</v>
       </c>
       <c r="C298" s="2" t="s">
@@ -5265,10 +6228,10 @@
       </c>
     </row>
     <row r="299" spans="1:3">
-      <c r="A299">
+      <c r="A299" s="0">
         <v>298</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B299" t="s" s="0">
         <v>303</v>
       </c>
       <c r="C299" s="2" t="s">
@@ -5276,10 +6239,10 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300">
+      <c r="A300" s="0">
         <v>299</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B300" t="s" s="0">
         <v>304</v>
       </c>
       <c r="C300" s="2" t="s">
@@ -5287,10 +6250,10 @@
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301">
+      <c r="A301" s="0">
         <v>300</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B301" t="s" s="0">
         <v>305</v>
       </c>
       <c r="C301" s="4" t="s">
@@ -5301,4 +6264,4234 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D301"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="39.0625" customWidth="true"/>
+    <col min="2" max="2" width="11.71875" customWidth="true"/>
+    <col min="3" max="3" width="17.578125" customWidth="true"/>
+    <col min="4" max="4" width="62.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>307</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C2" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C3" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C4" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>315</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C5" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C6" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C7" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>318</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C8" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C9" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C10" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C11" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C12" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="B13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C13" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="B14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C14" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>325</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C15" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="B16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C16" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="B17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C17" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="B18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C18" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="B19" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C19" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="B20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C20" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>331</v>
+      </c>
+      <c r="B21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C21" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>332</v>
+      </c>
+      <c r="B22" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C22" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="B23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C23" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>334</v>
+      </c>
+      <c r="B24" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C24" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="B25" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C25" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="B26" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C26" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="B27" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C27" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>338</v>
+      </c>
+      <c r="B28" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C28" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="B29" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C29" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="B30" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C30" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B31" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C31" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>342</v>
+      </c>
+      <c r="B32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C32" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="B33" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C33" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="B34" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C34" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="B35" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C35" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="B36" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C36" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="B37" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C37" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="B38" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C38" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="B39" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C39" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="B40" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C40" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="B41" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C41" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="B42" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C42" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="B43" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C43" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="B44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C44" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B45" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C45" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="B46" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C46" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="B47" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C47" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="B48" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C48" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="B49" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C49" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="B50" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C50" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="B51" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C51" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>362</v>
+      </c>
+      <c r="B52" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C52" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="B53" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C53" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="B54" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C54" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="B55" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C55" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="B56" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C56" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>367</v>
+      </c>
+      <c r="B57" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C57" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="B58" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C58" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="B59" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C59" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D59" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="B60" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C60" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>371</v>
+      </c>
+      <c r="B61" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C61" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D61" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="B62" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C62" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>373</v>
+      </c>
+      <c r="B63" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C63" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D63" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>374</v>
+      </c>
+      <c r="B64" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C64" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D64" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="B65" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C65" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D65" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="B66" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C66" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D66" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B67" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C67" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D67" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="B68" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C68" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B69" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C69" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D69" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="B70" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C70" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D70" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="B71" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C71" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D71" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="B72" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C72" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D72" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>383</v>
+      </c>
+      <c r="B73" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C73" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D73" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="B74" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C74" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D74" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="B75" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C75" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D75" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="B76" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C76" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D76" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>387</v>
+      </c>
+      <c r="B77" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C77" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D77" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="B78" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C78" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D78" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>389</v>
+      </c>
+      <c r="B79" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C79" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D79" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="B80" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C80" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D80" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="B81" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C81" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D81" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="B82" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C82" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D82" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C83" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D83" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>394</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C84" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D84" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>395</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C85" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D85" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>396</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C86" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D86" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>397</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C87" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D87" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C88" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D88" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>399</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C89" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D89" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C90" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>401</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C91" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>402</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C92" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D92" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>403</v>
+      </c>
+      <c r="B93" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C93" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D93" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="B94" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C94" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D94" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="B95" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C95" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D95" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="B96" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C96" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D96" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="B97" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C97" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D97" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="B98" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C98" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D98" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>409</v>
+      </c>
+      <c r="B99" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C99" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D99" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>410</v>
+      </c>
+      <c r="B100" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C100" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D100" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="B101" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C101" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D101" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="B102" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C102" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D102" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>413</v>
+      </c>
+      <c r="B103" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C103" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D103" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>414</v>
+      </c>
+      <c r="B104" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C104" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D104" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>415</v>
+      </c>
+      <c r="B105" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C105" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D105" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="B106" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C106" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D106" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>417</v>
+      </c>
+      <c r="B107" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C107" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D107" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>418</v>
+      </c>
+      <c r="B108" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C108" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D108" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="B109" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C109" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D109" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>420</v>
+      </c>
+      <c r="B110" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C110" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D110" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="B111" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C111" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D111" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>422</v>
+      </c>
+      <c r="B112" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C112" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D112" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="B113" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C113" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D113" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="B114" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C114" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D114" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>425</v>
+      </c>
+      <c r="B115" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C115" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D115" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="B116" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C116" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D116" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="B117" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C117" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="B118" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C118" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D118" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>429</v>
+      </c>
+      <c r="B119" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C119" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D119" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>430</v>
+      </c>
+      <c r="B120" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C120" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D120" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>431</v>
+      </c>
+      <c r="B121" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C121" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D121" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="B122" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C122" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D122" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>433</v>
+      </c>
+      <c r="B123" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C123" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D123" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>434</v>
+      </c>
+      <c r="B124" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C124" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D124" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="B125" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C125" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="B126" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C126" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D126" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="B127" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C127" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D127" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>438</v>
+      </c>
+      <c r="B128" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C128" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D128" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>439</v>
+      </c>
+      <c r="B129" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C129" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D129" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="B130" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C130" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D130" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>441</v>
+      </c>
+      <c r="B131" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C131" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D131" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>442</v>
+      </c>
+      <c r="B132" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C132" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D132" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>443</v>
+      </c>
+      <c r="B133" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C133" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D133" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>444</v>
+      </c>
+      <c r="B134" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C134" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D134" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="B135" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C135" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D135" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>446</v>
+      </c>
+      <c r="B136" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C136" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D136" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>447</v>
+      </c>
+      <c r="B137" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C137" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D137" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="B138" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C138" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D138" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>449</v>
+      </c>
+      <c r="B139" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C139" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D139" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="B140" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C140" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D140" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>451</v>
+      </c>
+      <c r="B141" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C141" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D141" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>452</v>
+      </c>
+      <c r="B142" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C142" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D142" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>453</v>
+      </c>
+      <c r="B143" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C143" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D143" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>454</v>
+      </c>
+      <c r="B144" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C144" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D144" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>455</v>
+      </c>
+      <c r="B145" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C145" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D145" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="B146" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C146" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D146" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>457</v>
+      </c>
+      <c r="B147" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C147" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D147" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>458</v>
+      </c>
+      <c r="B148" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C148" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D148" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>459</v>
+      </c>
+      <c r="B149" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C149" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D149" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>460</v>
+      </c>
+      <c r="B150" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C150" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D150" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>461</v>
+      </c>
+      <c r="B151" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C151" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D151" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>462</v>
+      </c>
+      <c r="B152" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C152" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D152" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>463</v>
+      </c>
+      <c r="B153" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C153" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D153" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="B154" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C154" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D154" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="B155" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C155" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D155" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="B156" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C156" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D156" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>467</v>
+      </c>
+      <c r="B157" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C157" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D157" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>468</v>
+      </c>
+      <c r="B158" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C158" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D158" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>469</v>
+      </c>
+      <c r="B159" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C159" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D159" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>470</v>
+      </c>
+      <c r="B160" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C160" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D160" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>471</v>
+      </c>
+      <c r="B161" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C161" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D161" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>472</v>
+      </c>
+      <c r="B162" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C162" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D162" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="B163" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C163" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D163" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="B164" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C164" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D164" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="B165" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C165" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D165" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>476</v>
+      </c>
+      <c r="B166" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C166" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D166" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="B167" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C167" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D167" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>478</v>
+      </c>
+      <c r="B168" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C168" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D168" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>479</v>
+      </c>
+      <c r="B169" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C169" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D169" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>480</v>
+      </c>
+      <c r="B170" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C170" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D170" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>481</v>
+      </c>
+      <c r="B171" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C171" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D171" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>482</v>
+      </c>
+      <c r="B172" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C172" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D172" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>483</v>
+      </c>
+      <c r="B173" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C173" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D173" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>484</v>
+      </c>
+      <c r="B174" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C174" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D174" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="B175" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C175" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D175" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>486</v>
+      </c>
+      <c r="B176" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C176" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D176" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>487</v>
+      </c>
+      <c r="B177" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C177" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D177" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>488</v>
+      </c>
+      <c r="B178" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C178" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D178" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>489</v>
+      </c>
+      <c r="B179" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C179" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D179" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="B180" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C180" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D180" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>491</v>
+      </c>
+      <c r="B181" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C181" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D181" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>492</v>
+      </c>
+      <c r="B182" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C182" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D182" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>493</v>
+      </c>
+      <c r="B183" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C183" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D183" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>494</v>
+      </c>
+      <c r="B184" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C184" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D184" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>495</v>
+      </c>
+      <c r="B185" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C185" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D185" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>496</v>
+      </c>
+      <c r="B186" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C186" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D186" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>497</v>
+      </c>
+      <c r="B187" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C187" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D187" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>498</v>
+      </c>
+      <c r="B188" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C188" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D188" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>499</v>
+      </c>
+      <c r="B189" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C189" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D189" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>500</v>
+      </c>
+      <c r="B190" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C190" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D190" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>501</v>
+      </c>
+      <c r="B191" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C191" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D191" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>502</v>
+      </c>
+      <c r="B192" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C192" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D192" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>503</v>
+      </c>
+      <c r="B193" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C193" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D193" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>504</v>
+      </c>
+      <c r="B194" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C194" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D194" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>505</v>
+      </c>
+      <c r="B195" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C195" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D195" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>506</v>
+      </c>
+      <c r="B196" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C196" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D196" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>507</v>
+      </c>
+      <c r="B197" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C197" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D197" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>508</v>
+      </c>
+      <c r="B198" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C198" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D198" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>509</v>
+      </c>
+      <c r="B199" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C199" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D199" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>510</v>
+      </c>
+      <c r="B200" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C200" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D200" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>511</v>
+      </c>
+      <c r="B201" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C201" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D201" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>512</v>
+      </c>
+      <c r="B202" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C202" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D202" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="B203" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C203" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D203" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>514</v>
+      </c>
+      <c r="B204" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C204" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D204" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>515</v>
+      </c>
+      <c r="B205" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C205" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D205" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>516</v>
+      </c>
+      <c r="B206" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C206" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D206" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>517</v>
+      </c>
+      <c r="B207" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C207" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D207" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>518</v>
+      </c>
+      <c r="B208" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C208" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D208" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>519</v>
+      </c>
+      <c r="B209" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C209" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D209" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="B210" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C210" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D210" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>521</v>
+      </c>
+      <c r="B211" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C211" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D211" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>522</v>
+      </c>
+      <c r="B212" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C212" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D212" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>523</v>
+      </c>
+      <c r="B213" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C213" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D213" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>524</v>
+      </c>
+      <c r="B214" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C214" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D214" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>525</v>
+      </c>
+      <c r="B215" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C215" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D215" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>526</v>
+      </c>
+      <c r="B216" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C216" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D216" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="B217" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C217" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D217" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="0">
+        <v>528</v>
+      </c>
+      <c r="B218" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C218" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D218" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="0">
+        <v>529</v>
+      </c>
+      <c r="B219" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C219" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D219" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="0">
+        <v>530</v>
+      </c>
+      <c r="B220" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C220" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D220" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="0">
+        <v>531</v>
+      </c>
+      <c r="B221" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C221" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D221" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="0">
+        <v>532</v>
+      </c>
+      <c r="B222" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C222" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D222" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="0">
+        <v>533</v>
+      </c>
+      <c r="B223" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C223" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D223" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="0">
+        <v>534</v>
+      </c>
+      <c r="B224" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C224" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D224" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="0">
+        <v>535</v>
+      </c>
+      <c r="B225" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C225" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D225" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="0">
+        <v>536</v>
+      </c>
+      <c r="B226" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C226" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D226" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="0">
+        <v>537</v>
+      </c>
+      <c r="B227" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C227" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D227" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>538</v>
+      </c>
+      <c r="B228" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C228" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D228" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>539</v>
+      </c>
+      <c r="B229" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C229" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D229" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>540</v>
+      </c>
+      <c r="B230" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C230" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D230" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="B231" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C231" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D231" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>542</v>
+      </c>
+      <c r="B232" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C232" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D232" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>543</v>
+      </c>
+      <c r="B233" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C233" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D233" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>544</v>
+      </c>
+      <c r="B234" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C234" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D234" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>545</v>
+      </c>
+      <c r="B235" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C235" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D235" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="0">
+        <v>546</v>
+      </c>
+      <c r="B236" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C236" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D236" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="0">
+        <v>547</v>
+      </c>
+      <c r="B237" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C237" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D237" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="0">
+        <v>548</v>
+      </c>
+      <c r="B238" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C238" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D238" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="0">
+        <v>549</v>
+      </c>
+      <c r="B239" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C239" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D239" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="0">
+        <v>550</v>
+      </c>
+      <c r="B240" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C240" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D240" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="0">
+        <v>551</v>
+      </c>
+      <c r="B241" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C241" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D241" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="0">
+        <v>552</v>
+      </c>
+      <c r="B242" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C242" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D242" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="0">
+        <v>553</v>
+      </c>
+      <c r="B243" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C243" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D243" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="0">
+        <v>554</v>
+      </c>
+      <c r="B244" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C244" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D244" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="0">
+        <v>555</v>
+      </c>
+      <c r="B245" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C245" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D245" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="0">
+        <v>556</v>
+      </c>
+      <c r="B246" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C246" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D246" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="0">
+        <v>557</v>
+      </c>
+      <c r="B247" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C247" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D247" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="0">
+        <v>558</v>
+      </c>
+      <c r="B248" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C248" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D248" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="0">
+        <v>559</v>
+      </c>
+      <c r="B249" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C249" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D249" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="0">
+        <v>560</v>
+      </c>
+      <c r="B250" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C250" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D250" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="0">
+        <v>561</v>
+      </c>
+      <c r="B251" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C251" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D251" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="0">
+        <v>562</v>
+      </c>
+      <c r="B252" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C252" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D252" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="0">
+        <v>563</v>
+      </c>
+      <c r="B253" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C253" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D253" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="0">
+        <v>564</v>
+      </c>
+      <c r="B254" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C254" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D254" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="0">
+        <v>565</v>
+      </c>
+      <c r="B255" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C255" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D255" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="0">
+        <v>566</v>
+      </c>
+      <c r="B256" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C256" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D256" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="0">
+        <v>567</v>
+      </c>
+      <c r="B257" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C257" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D257" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="0">
+        <v>568</v>
+      </c>
+      <c r="B258" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C258" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D258" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="B259" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C259" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D259" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="0">
+        <v>570</v>
+      </c>
+      <c r="B260" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C260" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D260" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="0">
+        <v>571</v>
+      </c>
+      <c r="B261" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C261" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D261" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="0">
+        <v>572</v>
+      </c>
+      <c r="B262" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C262" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D262" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="0">
+        <v>573</v>
+      </c>
+      <c r="B263" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C263" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D263" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="0">
+        <v>574</v>
+      </c>
+      <c r="B264" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C264" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D264" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="B265" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C265" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D265" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="0">
+        <v>576</v>
+      </c>
+      <c r="B266" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C266" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D266" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="0">
+        <v>577</v>
+      </c>
+      <c r="B267" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C267" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D267" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="0">
+        <v>578</v>
+      </c>
+      <c r="B268" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C268" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D268" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="0">
+        <v>579</v>
+      </c>
+      <c r="B269" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C269" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D269" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="0">
+        <v>580</v>
+      </c>
+      <c r="B270" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C270" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D270" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="0">
+        <v>581</v>
+      </c>
+      <c r="B271" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C271" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D271" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="0">
+        <v>582</v>
+      </c>
+      <c r="B272" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C272" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D272" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="0">
+        <v>583</v>
+      </c>
+      <c r="B273" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C273" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D273" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="0">
+        <v>584</v>
+      </c>
+      <c r="B274" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C274" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D274" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="0">
+        <v>585</v>
+      </c>
+      <c r="B275" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C275" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D275" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="0">
+        <v>586</v>
+      </c>
+      <c r="B276" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C276" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D276" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="0">
+        <v>587</v>
+      </c>
+      <c r="B277" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C277" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D277" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="0">
+        <v>588</v>
+      </c>
+      <c r="B278" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C278" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D278" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="0">
+        <v>589</v>
+      </c>
+      <c r="B279" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C279" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D279" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="B280" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C280" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D280" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="0">
+        <v>591</v>
+      </c>
+      <c r="B281" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C281" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D281" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="0">
+        <v>592</v>
+      </c>
+      <c r="B282" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C282" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D282" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="0">
+        <v>593</v>
+      </c>
+      <c r="B283" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C283" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D283" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="0">
+        <v>594</v>
+      </c>
+      <c r="B284" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C284" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D284" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="0">
+        <v>595</v>
+      </c>
+      <c r="B285" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C285" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D285" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="0">
+        <v>596</v>
+      </c>
+      <c r="B286" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C286" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D286" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="0">
+        <v>597</v>
+      </c>
+      <c r="B287" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C287" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D287" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="0">
+        <v>598</v>
+      </c>
+      <c r="B288" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C288" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D288" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="0">
+        <v>599</v>
+      </c>
+      <c r="B289" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C289" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D289" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="0">
+        <v>600</v>
+      </c>
+      <c r="B290" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C290" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D290" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="0">
+        <v>601</v>
+      </c>
+      <c r="B291" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C291" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D291" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="0">
+        <v>602</v>
+      </c>
+      <c r="B292" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C292" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D292" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="0">
+        <v>603</v>
+      </c>
+      <c r="B293" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C293" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D293" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="0">
+        <v>604</v>
+      </c>
+      <c r="B294" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C294" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D294" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="0">
+        <v>605</v>
+      </c>
+      <c r="B295" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C295" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D295" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="0">
+        <v>606</v>
+      </c>
+      <c r="B296" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C296" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D296" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="0">
+        <v>607</v>
+      </c>
+      <c r="B297" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C297" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D297" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="0">
+        <v>608</v>
+      </c>
+      <c r="B298" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C298" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D298" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="0">
+        <v>609</v>
+      </c>
+      <c r="B299" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C299" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D299" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="0">
+        <v>610</v>
+      </c>
+      <c r="B300" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C300" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D300" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="0">
+        <v>611</v>
+      </c>
+      <c r="B301" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C301" t="s" s="7">
+        <v>311</v>
+      </c>
+      <c r="D301" t="s" s="0">
+        <v>312</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/Domain.xlsx
+++ b/Domain.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2359348\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{16F5BF66-E53B-4190-9BC8-23A56D0DA251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F513C539-B2C2-4EA6-A77A-A5849B08E986}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F513C539-B2C2-4EA6-A77A-A5849B08E986}" activeTab="1" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="95">
   <si>
     <t>Domain</t>
   </si>
@@ -288,12 +289,49 @@
   </si>
   <si>
     <t>ymail.com</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>SAFE</t>
+  </si>
+  <si>
+    <t>Known legitimate provider</t>
+  </si>
+  <si>
+    <t>VALID DOMAIN</t>
+  </si>
+  <si>
+    <t>Has working MX/A record</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>INVALID</t>
+  </si>
+  <si>
+    <t>Bad domain syntax</t>
+  </si>
+  <si>
+    <t>TYPO</t>
+  </si>
+  <si>
+    <t>Likely typo of gmx.de</t>
+  </si>
+  <si>
+    <t>Likely typo of my.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -303,12 +341,52 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -323,11 +401,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,11 +747,11 @@
   <dimension ref="A1:A84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="25.6640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1096,6 +1178,945 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C84"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="39.0625" customWidth="true"/>
+    <col min="2" max="2" width="17.578125" customWidth="true"/>
+    <col min="3" max="3" width="62.5" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{d888dbc8-7820-46df-aafe-d03e984f84a5}" enabled="1" method="Standard" siteId="{8fc3a567-1ee8-4994-809c-49f50cdb6d48}" contentBits="1" removed="0"/>
